--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/76.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/76.xlsx
@@ -426,13 +426,13 @@
         <v>-11.00603104973569</v>
       </c>
       <c r="E2">
-        <v>-5.408100461049873</v>
+        <v>-4.12504792045663</v>
       </c>
       <c r="F2">
-        <v>-5.192902028245758</v>
+        <v>-5.224493475886322</v>
       </c>
       <c r="G2">
-        <v>-6.883568832291824</v>
+        <v>-7.314995816424106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.11304885743773</v>
       </c>
       <c r="E3">
-        <v>-6.348918106987435</v>
+        <v>-5.37684946192294</v>
       </c>
       <c r="F3">
-        <v>-5.183862054779007</v>
+        <v>-5.338560495619217</v>
       </c>
       <c r="G3">
-        <v>-6.531548593464501</v>
+        <v>-7.375184844873595</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.21368796544742</v>
       </c>
       <c r="E4">
-        <v>-6.348293177574377</v>
+        <v>-5.602725216951529</v>
       </c>
       <c r="F4">
-        <v>-5.504209125157034</v>
+        <v>-5.321242646696291</v>
       </c>
       <c r="G4">
-        <v>-6.722643213627852</v>
+        <v>-7.351564102450896</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.27712660687488</v>
       </c>
       <c r="E5">
-        <v>-7.555031874190359</v>
+        <v>-6.315719864037204</v>
       </c>
       <c r="F5">
-        <v>-5.397812787574063</v>
+        <v>-5.496285790949257</v>
       </c>
       <c r="G5">
-        <v>-6.698681485014607</v>
+        <v>-7.219291255429315</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.29680635117481</v>
       </c>
       <c r="E6">
-        <v>-9.205438754759827</v>
+        <v>-7.782737132718047</v>
       </c>
       <c r="F6">
-        <v>-5.235001316390834</v>
+        <v>-4.942790573216294</v>
       </c>
       <c r="G6">
-        <v>-6.525460500217781</v>
+        <v>-6.929502651649212</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.25335554048678</v>
       </c>
       <c r="E7">
-        <v>-8.914275989962654</v>
+        <v>-8.810229771162421</v>
       </c>
       <c r="F7">
-        <v>-5.509083238955107</v>
+        <v>-5.281266464204589</v>
       </c>
       <c r="G7">
-        <v>-6.283549006026618</v>
+        <v>-7.191442946352966</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.14632829332894</v>
       </c>
       <c r="E8">
-        <v>-10.47361072976387</v>
+        <v>-9.637369134085434</v>
       </c>
       <c r="F8">
-        <v>-5.19163628285428</v>
+        <v>-4.994266151993659</v>
       </c>
       <c r="G8">
-        <v>-6.026051463436565</v>
+        <v>-6.918253417906769</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.97467439287367</v>
       </c>
       <c r="E9">
-        <v>-11.59733796934524</v>
+        <v>-9.614088249212001</v>
       </c>
       <c r="F9">
-        <v>-5.284451536868353</v>
+        <v>-4.850500504135596</v>
       </c>
       <c r="G9">
-        <v>-6.002010281730378</v>
+        <v>-6.52378536417491</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.73581513064901</v>
       </c>
       <c r="E10">
-        <v>-11.9890328571127</v>
+        <v>-10.38106230646911</v>
       </c>
       <c r="F10">
-        <v>-4.992587051268184</v>
+        <v>-5.176087826703734</v>
       </c>
       <c r="G10">
-        <v>-6.168666454722829</v>
+        <v>-5.764826246569294</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.44255013364878</v>
       </c>
       <c r="E11">
-        <v>-11.98709919871142</v>
+        <v>-11.4361378800942</v>
       </c>
       <c r="F11">
-        <v>-4.796727034182866</v>
+        <v>-4.808142765360846</v>
       </c>
       <c r="G11">
-        <v>-5.562171201382808</v>
+        <v>-6.009803305929823</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.10584062412445</v>
       </c>
       <c r="E12">
-        <v>-13.69848651026818</v>
+        <v>-12.55537287345997</v>
       </c>
       <c r="F12">
-        <v>-4.555498162813622</v>
+        <v>-5.023560536826261</v>
       </c>
       <c r="G12">
-        <v>-4.902856193963716</v>
+        <v>-5.508255656730237</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.731730080785821</v>
       </c>
       <c r="E13">
-        <v>-13.21078344506411</v>
+        <v>-13.62786042964455</v>
       </c>
       <c r="F13">
-        <v>-4.608473914957457</v>
+        <v>-4.465431431842037</v>
       </c>
       <c r="G13">
-        <v>-4.499817137830685</v>
+        <v>-5.032536883828047</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.341580966129515</v>
       </c>
       <c r="E14">
-        <v>-15.03086318975297</v>
+        <v>-14.05991307776837</v>
       </c>
       <c r="F14">
-        <v>-4.359255439988211</v>
+        <v>-4.556189021227557</v>
       </c>
       <c r="G14">
-        <v>-4.840482205458307</v>
+        <v>-4.013226533377527</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.947612754318737</v>
       </c>
       <c r="E15">
-        <v>-16.12349339832367</v>
+        <v>-15.95174196463476</v>
       </c>
       <c r="F15">
-        <v>-4.495585662038745</v>
+        <v>-4.466608541921415</v>
       </c>
       <c r="G15">
-        <v>-4.033440724440316</v>
+        <v>-4.199054075587897</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.561158187717718</v>
       </c>
       <c r="E16">
-        <v>-16.56943487622901</v>
+        <v>-16.91501178470235</v>
       </c>
       <c r="F16">
-        <v>-4.080498211802538</v>
+        <v>-4.185051431914281</v>
       </c>
       <c r="G16">
-        <v>-3.654230975098959</v>
+        <v>-2.998133817944038</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.203392459439781</v>
       </c>
       <c r="E17">
-        <v>-17.96198591832772</v>
+        <v>-17.33833806341339</v>
       </c>
       <c r="F17">
-        <v>-4.122782225878439</v>
+        <v>-4.029630654698829</v>
       </c>
       <c r="G17">
-        <v>-2.239879846538287</v>
+        <v>-2.781875741136687</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.885352250157711</v>
       </c>
       <c r="E18">
-        <v>-18.36480726673202</v>
+        <v>-18.40538239384075</v>
       </c>
       <c r="F18">
-        <v>-3.424968010862344</v>
+        <v>-3.734274600495859</v>
       </c>
       <c r="G18">
-        <v>-3.253125277560862</v>
+        <v>-2.571510435389239</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.62129468590769</v>
       </c>
       <c r="E19">
-        <v>-19.57586159907731</v>
+        <v>-19.8207433595161</v>
       </c>
       <c r="F19">
-        <v>-3.568819808930297</v>
+        <v>-3.471895852598339</v>
       </c>
       <c r="G19">
-        <v>-2.215524163005869</v>
+        <v>-2.168302541433705</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.425982705351612</v>
       </c>
       <c r="E20">
-        <v>-19.75687829058592</v>
+        <v>-19.87232267846346</v>
       </c>
       <c r="F20">
-        <v>-3.222722109468844</v>
+        <v>-3.157499773642023</v>
       </c>
       <c r="G20">
-        <v>-2.087230591722493</v>
+        <v>-2.437247950498557</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.298828908194193</v>
       </c>
       <c r="E21">
-        <v>-21.06963309219547</v>
+        <v>-21.51327410530492</v>
       </c>
       <c r="F21">
-        <v>-2.923159605594459</v>
+        <v>-3.163658685281837</v>
       </c>
       <c r="G21">
-        <v>-1.905968291810777</v>
+        <v>-2.071730617507625</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.242630780879345</v>
       </c>
       <c r="E22">
-        <v>-22.54257360487835</v>
+        <v>-21.54205255762366</v>
       </c>
       <c r="F22">
-        <v>-2.890406786855169</v>
+        <v>-2.872415475233767</v>
       </c>
       <c r="G22">
-        <v>-2.263152981679363</v>
+        <v>-1.804351096482848</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.251808619684166</v>
       </c>
       <c r="E23">
-        <v>-21.84483085825051</v>
+        <v>-22.09446751639734</v>
       </c>
       <c r="F23">
-        <v>-2.902666624416602</v>
+        <v>-2.837293525722471</v>
       </c>
       <c r="G23">
-        <v>-2.090051176521952</v>
+        <v>-2.190334221997555</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.306698149559668</v>
       </c>
       <c r="E24">
-        <v>-22.98765920119624</v>
+        <v>-23.40558301041612</v>
       </c>
       <c r="F24">
-        <v>-2.59776694936598</v>
+        <v>-2.478402520092182</v>
       </c>
       <c r="G24">
-        <v>-2.387473898315614</v>
+        <v>-1.895977065373257</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.39280926058268</v>
       </c>
       <c r="E25">
-        <v>-22.54518653438078</v>
+        <v>-24.03431634164107</v>
       </c>
       <c r="F25">
-        <v>-2.757500207280406</v>
+        <v>-2.536712129942642</v>
       </c>
       <c r="G25">
-        <v>-2.425594830200322</v>
+        <v>-2.062484263816441</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.487761262747406</v>
       </c>
       <c r="E26">
-        <v>-24.09954448124756</v>
+        <v>-24.11825160737324</v>
       </c>
       <c r="F26">
-        <v>-2.183893057374874</v>
+        <v>-2.097946625864814</v>
       </c>
       <c r="G26">
-        <v>-2.387172638671541</v>
+        <v>-2.066645619559305</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.563418532950291</v>
       </c>
       <c r="E27">
-        <v>-24.21508849555327</v>
+        <v>-23.35332894884161</v>
       </c>
       <c r="F27">
-        <v>-2.399723355806882</v>
+        <v>-2.364795244267841</v>
       </c>
       <c r="G27">
-        <v>-3.596905568540939</v>
+        <v>-2.300797195006416</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.603884441510567</v>
       </c>
       <c r="E28">
-        <v>-23.66165463012786</v>
+        <v>-23.58058135996853</v>
       </c>
       <c r="F28">
-        <v>-2.541520802715894</v>
+        <v>-2.250807747805615</v>
       </c>
       <c r="G28">
-        <v>-3.393446060788411</v>
+        <v>-2.272051728088925</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.590419460147344</v>
       </c>
       <c r="E29">
-        <v>-23.64902471612046</v>
+        <v>-24.00638018548775</v>
       </c>
       <c r="F29">
-        <v>-2.519310615912033</v>
+        <v>-2.370258327289304</v>
       </c>
       <c r="G29">
-        <v>-3.293619870597227</v>
+        <v>-2.99753460920143</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.509451952625611</v>
       </c>
       <c r="E30">
-        <v>-22.85199064840044</v>
+        <v>-23.38463428965664</v>
       </c>
       <c r="F30">
-        <v>-2.567098303012134</v>
+        <v>-2.200045393362061</v>
       </c>
       <c r="G30">
-        <v>-2.638105369457218</v>
+        <v>-2.714241295769377</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.360991225380567</v>
       </c>
       <c r="E31">
-        <v>-23.20367193983612</v>
+        <v>-23.47229648949712</v>
       </c>
       <c r="F31">
-        <v>-2.570249412612383</v>
+        <v>-2.667629799383284</v>
       </c>
       <c r="G31">
-        <v>-3.208866594246346</v>
+        <v>-2.603960402765175</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.145264876759599</v>
       </c>
       <c r="E32">
-        <v>-22.96383489944188</v>
+        <v>-23.28618526472988</v>
       </c>
       <c r="F32">
-        <v>-2.598362545528593</v>
+        <v>-2.693165881309385</v>
       </c>
       <c r="G32">
-        <v>-3.167461601186681</v>
+        <v>-2.895857824053794</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.871910097015753</v>
       </c>
       <c r="E33">
-        <v>-21.40385258785758</v>
+        <v>-23.36541091749408</v>
       </c>
       <c r="F33">
-        <v>-2.368912230259755</v>
+        <v>-2.414794672333417</v>
       </c>
       <c r="G33">
-        <v>-3.060107230439195</v>
+        <v>-2.961277514455332</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.559288479041737</v>
       </c>
       <c r="E34">
-        <v>-22.37701259515792</v>
+        <v>-22.23415735411195</v>
       </c>
       <c r="F34">
-        <v>-2.465643176986861</v>
+        <v>-2.591217048312044</v>
       </c>
       <c r="G34">
-        <v>-3.175986255950304</v>
+        <v>-2.377535640606722</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.223291949276668</v>
       </c>
       <c r="E35">
-        <v>-21.43660704035506</v>
+        <v>-22.1445660243442</v>
       </c>
       <c r="F35">
-        <v>-2.807322364721782</v>
+        <v>-2.524584831165658</v>
       </c>
       <c r="G35">
-        <v>-2.694692524359981</v>
+        <v>-3.238492666277283</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.889259608133316</v>
       </c>
       <c r="E36">
-        <v>-20.00061887557477</v>
+        <v>-21.67752185756312</v>
       </c>
       <c r="F36">
-        <v>-2.596503689076711</v>
+        <v>-2.558324235481681</v>
       </c>
       <c r="G36">
-        <v>-3.407284141142565</v>
+        <v>-2.10813999734853</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.582648606771357</v>
       </c>
       <c r="E37">
-        <v>-20.80497548576519</v>
+        <v>-21.06221545177091</v>
       </c>
       <c r="F37">
-        <v>-2.461990905107919</v>
+        <v>-2.512952896095547</v>
       </c>
       <c r="G37">
-        <v>-3.496255052510477</v>
+        <v>-2.572348003410675</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.320070877981101</v>
       </c>
       <c r="E38">
-        <v>-19.79275286167469</v>
+        <v>-20.57686719305082</v>
       </c>
       <c r="F38">
-        <v>-2.584687028075776</v>
+        <v>-2.66174010714938</v>
       </c>
       <c r="G38">
-        <v>-2.742284927032543</v>
+        <v>-2.363247326059228</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.122235490705537</v>
       </c>
       <c r="E39">
-        <v>-20.14265446282535</v>
+        <v>-20.23136274016161</v>
       </c>
       <c r="F39">
-        <v>-2.30597038989284</v>
+        <v>-2.785373942017206</v>
       </c>
       <c r="G39">
-        <v>-2.494334997777749</v>
+        <v>-2.02115210275864</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.000288853354039</v>
       </c>
       <c r="E40">
-        <v>-19.69751905329338</v>
+        <v>-19.39692800561224</v>
       </c>
       <c r="F40">
-        <v>-2.430358039097213</v>
+        <v>-2.910654571281798</v>
       </c>
       <c r="G40">
-        <v>-1.631649867335688</v>
+        <v>-2.298082547664214</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.954705331594577</v>
       </c>
       <c r="E41">
-        <v>-18.77799429213988</v>
+        <v>-18.60262460771884</v>
       </c>
       <c r="F41">
-        <v>-2.405423351905546</v>
+        <v>-2.753469371498383</v>
       </c>
       <c r="G41">
-        <v>-2.20543693074771</v>
+        <v>-1.669946258133977</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.989740581212458</v>
       </c>
       <c r="E42">
-        <v>-18.0912647942987</v>
+        <v>-17.85528148528499</v>
       </c>
       <c r="F42">
-        <v>-2.279160278901234</v>
+        <v>-2.785634877749088</v>
       </c>
       <c r="G42">
-        <v>-1.81560695131637</v>
+        <v>-1.627753355235966</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.096851033610614</v>
       </c>
       <c r="E43">
-        <v>-16.9716584660643</v>
+        <v>-18.36388798650847</v>
       </c>
       <c r="F43">
-        <v>-2.894695244899463</v>
+        <v>-2.821262131376092</v>
       </c>
       <c r="G43">
-        <v>-2.433910920594971</v>
+        <v>-1.789741659018045</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.260904494298644</v>
       </c>
       <c r="E44">
-        <v>-17.1262198124201</v>
+        <v>-16.52889144843834</v>
       </c>
       <c r="F44">
-        <v>-2.870270832027919</v>
+        <v>-2.892556400265434</v>
       </c>
       <c r="G44">
-        <v>-1.748753794696328</v>
+        <v>-1.398945000289238</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.467449674786502</v>
       </c>
       <c r="E45">
-        <v>-16.41552563013032</v>
+        <v>-16.57317992423335</v>
       </c>
       <c r="F45">
-        <v>-2.927948397550043</v>
+        <v>-2.995172897389431</v>
       </c>
       <c r="G45">
-        <v>-1.665827939483124</v>
+        <v>-1.351713447080456</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.692724762223365</v>
       </c>
       <c r="E46">
-        <v>-16.77229239787661</v>
+        <v>-15.39183690985239</v>
       </c>
       <c r="F46">
-        <v>-2.896224411125031</v>
+        <v>-2.770119556294653</v>
       </c>
       <c r="G46">
-        <v>-1.59975276106481</v>
+        <v>-0.8842644169353643</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.920344545219992</v>
       </c>
       <c r="E47">
-        <v>-15.30141234086723</v>
+        <v>-14.87771472728756</v>
       </c>
       <c r="F47">
-        <v>-2.902363441947178</v>
+        <v>-2.909563611412311</v>
       </c>
       <c r="G47">
-        <v>-2.093477591155097</v>
+        <v>-0.9134369442274221</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.141289988768117</v>
       </c>
       <c r="E48">
-        <v>-14.71364358551566</v>
+        <v>-15.26209160105862</v>
       </c>
       <c r="F48">
-        <v>-3.108652604633741</v>
+        <v>-3.019860731095065</v>
       </c>
       <c r="G48">
-        <v>-2.038827105392809</v>
+        <v>-1.013776268977193</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.344741472344412</v>
       </c>
       <c r="E49">
-        <v>-13.4543111917746</v>
+        <v>-14.41185249222248</v>
       </c>
       <c r="F49">
-        <v>-3.003094574862403</v>
+        <v>-2.939748491202922</v>
       </c>
       <c r="G49">
-        <v>-2.612812801537186</v>
+        <v>-1.319078089154321</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.532743525854516</v>
       </c>
       <c r="E50">
-        <v>-13.15395109626784</v>
+        <v>-13.44458402960612</v>
       </c>
       <c r="F50">
-        <v>-2.727833885483947</v>
+        <v>-3.458241872697994</v>
       </c>
       <c r="G50">
-        <v>-1.995353021371099</v>
+        <v>-1.333558415343093</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.708913816444626</v>
       </c>
       <c r="E51">
-        <v>-13.15002038082918</v>
+        <v>-12.44689327860622</v>
       </c>
       <c r="F51">
-        <v>-2.897526604682231</v>
+        <v>-3.177517271930673</v>
       </c>
       <c r="G51">
-        <v>-2.770437806298506</v>
+        <v>-1.320776399015967</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.874280395247036</v>
       </c>
       <c r="E52">
-        <v>-13.0321306169875</v>
+        <v>-12.08340172695854</v>
       </c>
       <c r="F52">
-        <v>-3.277450687037002</v>
+        <v>-3.189396060486818</v>
       </c>
       <c r="G52">
-        <v>-3.183948117972252</v>
+        <v>-1.412412299542993</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.04084807964492</v>
       </c>
       <c r="E53">
-        <v>-12.65752166165099</v>
+        <v>-11.81289786058436</v>
       </c>
       <c r="F53">
-        <v>-3.532225022176823</v>
+        <v>-3.208489100753943</v>
       </c>
       <c r="G53">
-        <v>-1.660382092071023</v>
+        <v>-1.272621203601728</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.213919559956575</v>
       </c>
       <c r="E54">
-        <v>-11.79259671160797</v>
+        <v>-10.79518672599655</v>
       </c>
       <c r="F54">
-        <v>-3.203472507762589</v>
+        <v>-3.465952316483252</v>
       </c>
       <c r="G54">
-        <v>-2.375479791826835</v>
+        <v>-1.344592463625484</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.393237083006666</v>
       </c>
       <c r="E55">
-        <v>-11.83662253591054</v>
+        <v>-10.29992563767368</v>
       </c>
       <c r="F55">
-        <v>-3.019511988418487</v>
+        <v>-3.428162195567539</v>
       </c>
       <c r="G55">
-        <v>-2.998709852867871</v>
+        <v>-1.127956984626656</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.583403938537635</v>
       </c>
       <c r="E56">
-        <v>-11.09964961895425</v>
+        <v>-9.521879461467817</v>
       </c>
       <c r="F56">
-        <v>-3.254103151789098</v>
+        <v>-3.612550980858889</v>
       </c>
       <c r="G56">
-        <v>-2.58045552943635</v>
+        <v>-1.680980306416368</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.779168896559156</v>
       </c>
       <c r="E57">
-        <v>-10.56411228280716</v>
+        <v>-9.945355179821103</v>
       </c>
       <c r="F57">
-        <v>-3.471741776261418</v>
+        <v>-3.701792657897285</v>
       </c>
       <c r="G57">
-        <v>-2.66771488876046</v>
+        <v>-1.559387279304477</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.974094904104474</v>
       </c>
       <c r="E58">
-        <v>-10.56937889807808</v>
+        <v>-8.608862117463342</v>
       </c>
       <c r="F58">
-        <v>-3.118067000166558</v>
+        <v>-3.746454086419221</v>
       </c>
       <c r="G58">
-        <v>-3.056108091427755</v>
+        <v>-1.508461157273868</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.168165269548526</v>
       </c>
       <c r="E59">
-        <v>-9.720466632126186</v>
+        <v>-8.585413679051625</v>
       </c>
       <c r="F59">
-        <v>-3.441259512573202</v>
+        <v>-3.750418652809019</v>
       </c>
       <c r="G59">
-        <v>-2.808403142542867</v>
+        <v>-1.479285319436271</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.354020541482894</v>
       </c>
       <c r="E60">
-        <v>-8.691144490182714</v>
+        <v>-7.646814985377821</v>
       </c>
       <c r="F60">
-        <v>-3.542329447756172</v>
+        <v>-3.550335618704229</v>
       </c>
       <c r="G60">
-        <v>-2.637320770164411</v>
+        <v>-1.588957072061247</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.531488265611053</v>
       </c>
       <c r="E61">
-        <v>-8.670295395851399</v>
+        <v>-7.533671062296177</v>
       </c>
       <c r="F61">
-        <v>-3.791287815360938</v>
+        <v>-3.605352468128561</v>
       </c>
       <c r="G61">
-        <v>-3.124043796439139</v>
+        <v>-2.060646911042145</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.705192838957089</v>
       </c>
       <c r="E62">
-        <v>-8.483151679010414</v>
+        <v>-7.05413736420194</v>
       </c>
       <c r="F62">
-        <v>-3.586551013187221</v>
+        <v>-3.636086555507228</v>
       </c>
       <c r="G62">
-        <v>-2.784785710665707</v>
+        <v>-2.075332491054352</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.872113553980617</v>
       </c>
       <c r="E63">
-        <v>-8.567893013115949</v>
+        <v>-6.249300735766703</v>
       </c>
       <c r="F63">
-        <v>-3.620918319994567</v>
+        <v>-3.688300209640487</v>
       </c>
       <c r="G63">
-        <v>-3.619715227306518</v>
+        <v>-2.773281564916739</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.039302273136897</v>
       </c>
       <c r="E64">
-        <v>-8.321938004337349</v>
+        <v>-6.857234785874425</v>
       </c>
       <c r="F64">
-        <v>-3.447160801950745</v>
+        <v>-3.973609823982304</v>
       </c>
       <c r="G64">
-        <v>-2.738411588751596</v>
+        <v>-2.492868426103852</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.210481834988336</v>
       </c>
       <c r="E65">
-        <v>-7.753406206570366</v>
+        <v>-6.763993506056493</v>
       </c>
       <c r="F65">
-        <v>-3.624592957793385</v>
+        <v>-3.835516836098612</v>
       </c>
       <c r="G65">
-        <v>-3.861219524396351</v>
+        <v>-2.466072870508991</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.378011801471681</v>
       </c>
       <c r="E66">
-        <v>-7.498194996920088</v>
+        <v>-6.568847975643954</v>
       </c>
       <c r="F66">
-        <v>-3.786122116237081</v>
+        <v>-3.370366173506814</v>
       </c>
       <c r="G66">
-        <v>-3.932207552394943</v>
+        <v>-3.011445521557448</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.542453495783748</v>
       </c>
       <c r="E67">
-        <v>-7.243921181389397</v>
+        <v>-5.096672775068375</v>
       </c>
       <c r="F67">
-        <v>-3.781045880792725</v>
+        <v>-3.871937665697498</v>
       </c>
       <c r="G67">
-        <v>-3.393439439697332</v>
+        <v>-2.698400335363965</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.696564195029705</v>
       </c>
       <c r="E68">
-        <v>-8.525547252670224</v>
+        <v>-5.698620182537956</v>
       </c>
       <c r="F68">
-        <v>-3.445955527379672</v>
+        <v>-3.793207971000628</v>
       </c>
       <c r="G68">
-        <v>-3.85422765221741</v>
+        <v>-2.75342822331773</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.827497525177508</v>
       </c>
       <c r="E69">
-        <v>-6.730482798399732</v>
+        <v>-5.221069956059079</v>
       </c>
       <c r="F69">
-        <v>-3.904332629718779</v>
+        <v>-3.879361494361387</v>
       </c>
       <c r="G69">
-        <v>-3.768997657308874</v>
+        <v>-2.711523337881635</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.93342919552998</v>
       </c>
       <c r="E70">
-        <v>-7.741881240220845</v>
+        <v>-5.202969645450421</v>
       </c>
       <c r="F70">
-        <v>-3.993647203088621</v>
+        <v>-3.596678633053847</v>
       </c>
       <c r="G70">
-        <v>-4.300151515266161</v>
+        <v>-2.755146396452612</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.00561544331688</v>
       </c>
       <c r="E71">
-        <v>-7.405347694340822</v>
+        <v>-5.494091653981525</v>
       </c>
       <c r="F71">
-        <v>-3.790848780637455</v>
+        <v>-3.924010497372281</v>
       </c>
       <c r="G71">
-        <v>-3.585758961710213</v>
+        <v>-3.085760647823007</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.03547235510239</v>
       </c>
       <c r="E72">
-        <v>-7.067804298757089</v>
+        <v>-5.011596333886271</v>
       </c>
       <c r="F72">
-        <v>-3.903154691271998</v>
+        <v>-3.801323486445854</v>
       </c>
       <c r="G72">
-        <v>-3.77982645176783</v>
+        <v>-2.913416957594089</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.02721884748815</v>
       </c>
       <c r="E73">
-        <v>-7.974893870285523</v>
+        <v>-5.540626252884346</v>
       </c>
       <c r="F73">
-        <v>-3.904926569146586</v>
+        <v>-3.984642021052788</v>
       </c>
       <c r="G73">
-        <v>-3.683761041309258</v>
+        <v>-2.698976370287797</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.978554308364712</v>
       </c>
       <c r="E74">
-        <v>-7.602209516402268</v>
+        <v>-5.288634788253521</v>
       </c>
       <c r="F74">
-        <v>-3.987303565517982</v>
+        <v>-4.099082634484345</v>
       </c>
       <c r="G74">
-        <v>-3.756116324615569</v>
+        <v>-2.5373489159695</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.892431485182527</v>
       </c>
       <c r="E75">
-        <v>-7.571266453507857</v>
+        <v>-5.520592283874412</v>
       </c>
       <c r="F75">
-        <v>-3.816379892359138</v>
+        <v>-4.079712919504684</v>
       </c>
       <c r="G75">
-        <v>-3.722282549204218</v>
+        <v>-2.204231892171415</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.779448548927901</v>
       </c>
       <c r="E76">
-        <v>-8.668683259104668</v>
+        <v>-6.022564570676656</v>
       </c>
       <c r="F76">
-        <v>-4.13378708682463</v>
+        <v>-4.387388453722088</v>
       </c>
       <c r="G76">
-        <v>-2.668641841511456</v>
+        <v>-1.809177871879106</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.643023984189783</v>
       </c>
       <c r="E77">
-        <v>-7.986604504069359</v>
+        <v>-7.43398576396533</v>
       </c>
       <c r="F77">
-        <v>-3.935852837762702</v>
+        <v>-4.57385809792927</v>
       </c>
       <c r="G77">
-        <v>-2.10023441460075</v>
+        <v>-1.795737056989665</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.495318693765261</v>
       </c>
       <c r="E78">
-        <v>-8.552351290321624</v>
+        <v>-7.653132206618522</v>
       </c>
       <c r="F78">
-        <v>-4.314232014911252</v>
+        <v>-4.294748813597407</v>
       </c>
       <c r="G78">
-        <v>-2.758675437997475</v>
+        <v>-1.862444549605979</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.348986040581872</v>
       </c>
       <c r="E79">
-        <v>-11.01746234418905</v>
+        <v>-7.694214522816107</v>
       </c>
       <c r="F79">
-        <v>-4.421214836615405</v>
+        <v>-4.191606303172633</v>
       </c>
       <c r="G79">
-        <v>-1.816507419703052</v>
+        <v>-1.140940944231677</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.205990143189929</v>
       </c>
       <c r="E80">
-        <v>-10.57879359554003</v>
+        <v>-8.219078245727124</v>
       </c>
       <c r="F80">
-        <v>-4.440842173857337</v>
+        <v>-4.637224062406418</v>
       </c>
       <c r="G80">
-        <v>-2.600242660124573</v>
+        <v>-1.17953859467404</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.079023077708037</v>
       </c>
       <c r="E81">
-        <v>-9.374862552808798</v>
+        <v>-8.640919184963641</v>
       </c>
       <c r="F81">
-        <v>-4.732875646407678</v>
+        <v>-4.763830907882892</v>
       </c>
       <c r="G81">
-        <v>-2.51063943455866</v>
+        <v>-1.016706101779447</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.973667800464895</v>
       </c>
       <c r="E82">
-        <v>-11.47856968154607</v>
+        <v>-9.382909651120428</v>
       </c>
       <c r="F82">
-        <v>-4.632732654348439</v>
+        <v>-4.533912565031472</v>
       </c>
       <c r="G82">
-        <v>-2.686505545241363</v>
+        <v>-0.4153554362074541</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.88654590855872</v>
       </c>
       <c r="E83">
-        <v>-12.37900692475724</v>
+        <v>-11.13759823113853</v>
       </c>
       <c r="F83">
-        <v>-4.695005173853892</v>
+        <v>-5.04498046112785</v>
       </c>
       <c r="G83">
-        <v>-1.92062738745867</v>
+        <v>-0.7755163065158451</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.826625583488303</v>
       </c>
       <c r="E84">
-        <v>-13.00032261555763</v>
+        <v>-12.16478746182439</v>
       </c>
       <c r="F84">
-        <v>-4.771401357577077</v>
+        <v>-5.051500540955285</v>
       </c>
       <c r="G84">
-        <v>-1.952819132282543</v>
+        <v>-0.5727420816899457</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.795048951263695</v>
       </c>
       <c r="E85">
-        <v>-14.42940485747621</v>
+        <v>-12.88951085658993</v>
       </c>
       <c r="F85">
-        <v>-5.062483035981601</v>
+        <v>-5.128492320841082</v>
       </c>
       <c r="G85">
-        <v>-1.671565114902681</v>
+        <v>-0.3977036073920602</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.788901812302759</v>
       </c>
       <c r="E86">
-        <v>-15.31877903868664</v>
+        <v>-14.37594169334166</v>
       </c>
       <c r="F86">
-        <v>-4.79794721936719</v>
+        <v>-5.161061242016951</v>
       </c>
       <c r="G86">
-        <v>-1.543188779980823</v>
+        <v>0.288158664706448</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.815633004166072</v>
       </c>
       <c r="E87">
-        <v>-16.59072323253907</v>
+        <v>-15.37576535559917</v>
       </c>
       <c r="F87">
-        <v>-4.92834053224186</v>
+        <v>-5.166843246488491</v>
       </c>
       <c r="G87">
-        <v>-1.250596144128957</v>
+        <v>-0.0622427173521715</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.870936573165107</v>
       </c>
       <c r="E88">
-        <v>-18.4655748703507</v>
+        <v>-17.18648021604017</v>
       </c>
       <c r="F88">
-        <v>-5.194629174280594</v>
+        <v>-5.404210269025883</v>
       </c>
       <c r="G88">
-        <v>-1.32103131102249</v>
+        <v>0.2996760526375725</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.952932063507008</v>
       </c>
       <c r="E89">
-        <v>-19.92468995188816</v>
+        <v>-18.82728220323937</v>
       </c>
       <c r="F89">
-        <v>-5.489408684771216</v>
+        <v>-5.478988651211401</v>
       </c>
       <c r="G89">
-        <v>-1.795005426425486</v>
+        <v>0.06919918273905171</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.06468846241939</v>
       </c>
       <c r="E90">
-        <v>-21.29451711141638</v>
+        <v>-20.06218800818306</v>
       </c>
       <c r="F90">
-        <v>-5.446912608640198</v>
+        <v>-5.41136404991646</v>
       </c>
       <c r="G90">
-        <v>-2.146774063791824</v>
+        <v>0.6128337973793911</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.197028951272626</v>
       </c>
       <c r="E91">
-        <v>-24.37751580126039</v>
+        <v>-21.9463139607624</v>
       </c>
       <c r="F91">
-        <v>-5.01394070617755</v>
+        <v>-5.396935546494499</v>
       </c>
       <c r="G91">
-        <v>-1.164449128106042</v>
+        <v>-0.2446339132927783</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.347375964673491</v>
       </c>
       <c r="E92">
-        <v>-25.53825878738046</v>
+        <v>-24.81584491435883</v>
       </c>
       <c r="F92">
-        <v>-5.276239102436999</v>
+        <v>-5.514767496073117</v>
       </c>
       <c r="G92">
-        <v>-1.886320204035203</v>
+        <v>-0.173801480934532</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.511441329620249</v>
       </c>
       <c r="E93">
-        <v>-27.56775328408003</v>
+        <v>-26.89896107178323</v>
       </c>
       <c r="F93">
-        <v>-5.310037320838622</v>
+        <v>-5.442147839339295</v>
       </c>
       <c r="G93">
-        <v>-2.39112874059097</v>
+        <v>-0.5422552678187973</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.67297036002417</v>
       </c>
       <c r="E94">
-        <v>-30.20356742990359</v>
+        <v>-28.97974506509367</v>
       </c>
       <c r="F94">
-        <v>-5.316726387616228</v>
+        <v>-5.478760850175631</v>
       </c>
       <c r="G94">
-        <v>-2.346072215801489</v>
+        <v>-0.5664884611662624</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.827797018311921</v>
       </c>
       <c r="E95">
-        <v>-31.83045115224022</v>
+        <v>-31.49372288197786</v>
       </c>
       <c r="F95">
-        <v>-5.284732353417903</v>
+        <v>-5.578574152008555</v>
       </c>
       <c r="G95">
-        <v>-2.839664624070205</v>
+        <v>-0.5722256365858194</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.963806389301169</v>
       </c>
       <c r="E96">
-        <v>-33.62249737858459</v>
+        <v>-33.74609981238695</v>
       </c>
       <c r="F96">
-        <v>-5.432321745207288</v>
+        <v>-5.637272266170927</v>
       </c>
       <c r="G96">
-        <v>-3.865572891780492</v>
+        <v>-1.292990990304864</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.0657576100382</v>
       </c>
       <c r="E97">
-        <v>-36.26705600771697</v>
+        <v>-36.65180421635665</v>
       </c>
       <c r="F97">
-        <v>-5.737206509644659</v>
+        <v>-5.647973116280292</v>
       </c>
       <c r="G97">
-        <v>-3.270892975470131</v>
+        <v>-1.629173579272313</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.12672497743909</v>
       </c>
       <c r="E98">
-        <v>-39.83569277861754</v>
+        <v>-39.14449594116779</v>
       </c>
       <c r="F98">
-        <v>-5.490092087878526</v>
+        <v>-5.597055857132414</v>
       </c>
       <c r="G98">
-        <v>-4.30101887819745</v>
+        <v>-2.379171050103122</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.14552495084826</v>
       </c>
       <c r="E99">
-        <v>-42.68960502536152</v>
+        <v>-42.17693195447915</v>
       </c>
       <c r="F99">
-        <v>-6.111503492232213</v>
+        <v>-5.950283314829763</v>
       </c>
       <c r="G99">
-        <v>-4.378621376183506</v>
+        <v>-2.792429760315884</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.1072303154474</v>
       </c>
       <c r="E100">
-        <v>-44.85355670805983</v>
+        <v>-44.18914579436545</v>
       </c>
       <c r="F100">
-        <v>-5.470646163097807</v>
+        <v>-5.779420940858725</v>
       </c>
       <c r="G100">
-        <v>-4.857405714255061</v>
+        <v>-3.334180674544378</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.03406127273802</v>
       </c>
       <c r="E101">
-        <v>-47.43205395836831</v>
+        <v>-47.45378384089411</v>
       </c>
       <c r="F101">
-        <v>-5.950210418498316</v>
+        <v>-5.855402112513107</v>
       </c>
       <c r="G101">
-        <v>-5.462262247553143</v>
+        <v>-3.948008786253884</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.9024276020403</v>
       </c>
       <c r="E102">
-        <v>-49.62576790436353</v>
+        <v>-49.20424735466306</v>
       </c>
       <c r="F102">
-        <v>-5.529282978072373</v>
+        <v>-5.835097999103088</v>
       </c>
       <c r="G102">
-        <v>-6.20554924257585</v>
+        <v>-4.133561553184495</v>
       </c>
     </row>
   </sheetData>
